--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/COLORADO_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/COLORADO_2017.xlsx
@@ -1453,7 +1453,7 @@
         <v>15</v>
       </c>
       <c r="D61">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="62">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C137">
@@ -3217,7 +3217,7 @@
         <v>15</v>
       </c>
       <c r="D159">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="160">
@@ -3487,7 +3487,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="175">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C185">
@@ -3811,7 +3811,7 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="193">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C301">
@@ -6259,7 +6259,7 @@
         <v>142</v>
       </c>
       <c r="D328">
-        <v>0.009035377958768135</v>
+        <v>0.009035377958768137</v>
       </c>
     </row>
     <row r="329">
@@ -6331,7 +6331,7 @@
         <v>15</v>
       </c>
       <c r="D332">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="333">
@@ -11911,7 +11911,7 @@
         <v>15</v>
       </c>
       <c r="D642">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="643">
@@ -13819,7 +13819,7 @@
         <v>15</v>
       </c>
       <c r="D748">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="749">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C778">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C779">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C822">
@@ -18643,7 +18643,7 @@
         <v>15</v>
       </c>
       <c r="D1016">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="1017">
@@ -19579,7 +19579,7 @@
         <v>15</v>
       </c>
       <c r="D1068">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="1069">
@@ -21091,7 +21091,7 @@
         <v>15</v>
       </c>
       <c r="D1152">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="1153">
@@ -21397,7 +21397,7 @@
         <v>15</v>
       </c>
       <c r="D1169">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="1170">
@@ -23161,7 +23161,7 @@
         <v>15</v>
       </c>
       <c r="D1267">
-        <v>0.0009544413336726903</v>
+        <v>0.0009544413336726904</v>
       </c>
     </row>
     <row r="1268">
